--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/4912-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/4912-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A15D5CE5-5ED9-4136-99DA-C6652608555A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DAAC76C2-00A9-431A-B935-D80CF80F64CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{3ED5F810-DB98-4B87-9746-8BE8F5701C3D}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{C7C194BE-70BD-4921-A406-DEB54C3A3DC6}"/>
   </bookViews>
   <sheets>
     <sheet name="4912-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1610,25 +1610,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF4F29BA-F008-4D37-8C25-E7C55AF50A84}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1057A849-0F64-44FC-80F2-FD11768851A5}">
   <dimension ref="A1:R51"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.77734375" customWidth="1"/>
-    <col min="2" max="2" width="10.109375" customWidth="1"/>
-    <col min="3" max="3" width="7.44140625" customWidth="1"/>
-    <col min="4" max="4" width="7.77734375" customWidth="1"/>
-    <col min="5" max="5" width="7.44140625" customWidth="1"/>
-    <col min="6" max="7" width="7.77734375" customWidth="1"/>
-    <col min="8" max="8" width="7.44140625" customWidth="1"/>
-    <col min="9" max="10" width="7.77734375" customWidth="1"/>
-    <col min="11" max="13" width="7.44140625" customWidth="1"/>
-    <col min="14" max="14" width="7.77734375" customWidth="1"/>
-    <col min="15" max="17" width="7.44140625" customWidth="1"/>
-    <col min="18" max="18" width="8.33203125" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="13.375" customWidth="1"/>
+    <col min="3" max="3" width="9.875" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="7" width="10.375" customWidth="1"/>
+    <col min="8" max="8" width="9.875" customWidth="1"/>
+    <col min="9" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1656,7 +1656,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1686,7 +1686,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1732,7 +1732,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1782,7 +1782,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2025</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>1.69</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1892,7 +1892,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>25</v>
       </c>
@@ -2004,7 +2004,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>25</v>
       </c>
@@ -2060,7 +2060,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="41">
         <v>2024</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>2.13</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
@@ -2170,7 +2170,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
@@ -2226,7 +2226,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>25</v>
       </c>
@@ -2282,7 +2282,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>25</v>
       </c>
@@ -2338,7 +2338,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="39">
         <v>2023</v>
       </c>
@@ -2392,7 +2392,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>25</v>
       </c>
@@ -2448,7 +2448,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
@@ -2504,7 +2504,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2560,7 +2560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2616,7 +2616,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="41">
         <v>2022</v>
       </c>
@@ -2670,7 +2670,7 @@
         <v>3.13</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
@@ -2726,7 +2726,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2782,7 +2782,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>25</v>
       </c>
@@ -2838,7 +2838,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>25</v>
       </c>
@@ -2894,7 +2894,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="39">
         <v>2021</v>
       </c>
@@ -2948,7 +2948,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>25</v>
       </c>
@@ -3004,7 +3004,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>25</v>
       </c>
@@ -3060,7 +3060,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>25</v>
       </c>
@@ -3116,7 +3116,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="43" t="s">
         <v>25</v>
       </c>
@@ -3172,7 +3172,7 @@
         <v>2.4900000000000002</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="44"/>
       <c r="B30" s="22" t="s">
         <v>64</v>
@@ -3194,7 +3194,7 @@
       <c r="Q30" s="48"/>
       <c r="R30" s="48"/>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>25</v>
       </c>
@@ -3250,7 +3250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="41">
         <v>2020</v>
       </c>
@@ -3304,7 +3304,7 @@
         <v>3.68</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>25</v>
       </c>
@@ -3360,7 +3360,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
         <v>25</v>
       </c>
@@ -3416,7 +3416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
         <v>25</v>
       </c>
@@ -3472,7 +3472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="17" t="s">
         <v>25</v>
       </c>
@@ -3528,7 +3528,7 @@
         <v>2.83</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="39">
         <v>2019</v>
       </c>
@@ -3582,7 +3582,7 @@
         <v>3.18</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
         <v>25</v>
       </c>
@@ -3638,7 +3638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>25</v>
       </c>
@@ -3694,7 +3694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
         <v>25</v>
       </c>
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
         <v>25</v>
       </c>
@@ -3806,7 +3806,7 @@
         <v>3.18</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="41">
         <v>2018</v>
       </c>
@@ -3860,7 +3860,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="39">
         <v>2017</v>
       </c>
@@ -3914,7 +3914,7 @@
         <v>2.02</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="41">
         <v>2016</v>
       </c>
@@ -3968,7 +3968,7 @@
         <v>6.94</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="39">
         <v>2015</v>
       </c>
@@ -4022,7 +4022,7 @@
         <v>6.62</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="41">
         <v>2014</v>
       </c>
@@ -4076,7 +4076,7 @@
         <v>4.9800000000000004</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="39">
         <v>2013</v>
       </c>
@@ -4130,7 +4130,7 @@
         <v>8.56</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="41">
         <v>2012</v>
       </c>
@@ -4184,7 +4184,7 @@
         <v>3.95</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="39">
         <v>2011</v>
       </c>
@@ -4238,7 +4238,7 @@
         <v>3.42</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="41">
         <v>2010</v>
       </c>
@@ -4292,7 +4292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="39" t="s">
         <v>76</v>
       </c>
